--- a/technology_surveys/004_public_awareness_of_sustainable_tourism_survey--technology_surveys.xlsx
+++ b/technology_surveys/004_public_awareness_of_sustainable_tourism_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -964,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_high'}</t>
+          <t>somewhat_high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat High'}</t>
+          <t>Somewhat High</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_low'}</t>
+          <t>somewhat_low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Low'}</t>
+          <t>Somewhat Low</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_low'}</t>
+          <t>very_low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Low'}</t>
+          <t>Very Low</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'environmental'}</t>
+          <t>environmental</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Environmental'}</t>
+          <t>Environmental</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'social'}</t>
+          <t>social</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Social'}</t>
+          <t>Social</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'economic'}</t>
+          <t>economic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Economic'}</t>
+          <t>Economic</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'cultural'}</t>
+          <t>cultural</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Cultural'}</t>
+          <t>Cultural</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'bachelor'}</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Bachelor'}</t>
+          <t>Bachelor</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'masters'}</t>
+          <t>masters</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Masters'}</t>
+          <t>Masters</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'phd'}</t>
+          <t>phd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'PhD'}</t>
+          <t>PhD</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'others'}</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Others'}</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'I agree'}</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'i_disagree'}</t>
+          <t>i_disagree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'I disagree'}</t>
+          <t>I disagree</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'neither_agree_nor_disagree'}</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Neither agree nor disagree'}</t>
+          <t>Neither agree nor disagree</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_unsatisfied'}</t>
+          <t>somewhat_unsatisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Unsatisfied'}</t>
+          <t>Somewhat Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'very_unsatisfied'}</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Very Unsatisfied'}</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'1-5_times_a_year'}</t>
+          <t>1-5_times_a_year</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': '1-5 times a year'}</t>
+          <t>1-5 times a year</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'6-10_times_a_year'}</t>
+          <t>6-10_times_a_year</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': '6-10 times a year'}</t>
+          <t>6-10 times a year</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'11-20_times_a_year'}</t>
+          <t>11-20_times_a_year</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': '11-20 times a year'}</t>
+          <t>11-20 times a year</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'21-30_times_a_year'}</t>
+          <t>21-30_times_a_year</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': '21-30 times a year'}</t>
+          <t>21-30 times a year</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_30_times_a_year'}</t>
+          <t>more_than_30_times_a_year</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'More than 30 times a year'}</t>
+          <t>More than 30 times a year</t>
         </is>
       </c>
     </row>
